--- a/internal/importer/parser/testdata/sbi_v1.xlsx
+++ b/internal/importer/parser/testdata/sbi_v1.xlsx
@@ -413,364 +413,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Mr. Rahul  Sharma</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ref No/Cheque No</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Balance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SAMPLE STREET</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OPP.POST OFFICE</t>
-        </is>
+          <t xml:space="preserve"> DEP TFR SBI General Insurance Co Ltd SBIGEN 99900000001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14364.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Date of Statement  :  10-05-2026</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Branch Code  :  9999</t>
-        </is>
+          <t xml:space="preserve"> WDL TFR PMSBY RENEWAL SBISB09999990000000001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14344.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clear Balance  :  14454.59CR</t>
+          <t>25/06/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Branch Name  :  SAMPLE BRANCH</t>
-        </is>
+          <t xml:space="preserve"> INTEREST CREDIT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>97</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14441.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uncleared Amount  :  0.00</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Branch Email ID  :  sbi.01222@sbi.co.in</t>
-        </is>
+          <t xml:space="preserve"> DEBIT ATMCard AMC 999999*0000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>236</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14205.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MOD Bal   :  0.00</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Branch Phone   :  0000000000</t>
-        </is>
+          <t xml:space="preserve"> INTEREST CREDIT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>91</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14296.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lien  :  0.00</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIF Number  :  90000000001</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Limit  :  0.00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Account Number  :  40000000001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Monthly Avg Balance  :  0.00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Product  :  Savings Account</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Interest Rate  :  2.50 % p.a.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>IFSC Code  :  SBIN0001000</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Drawing Power  :  0.00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Currency  :  INR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Account Status  :  OPEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CKYCR Number  :  30000000000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MICR Code  :  000000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Account Open Date  :  26/08/2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Nominee  Name  :  XXXXXXXXXXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Statement From  :  01-04-2025  to  10-05-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ref No/Cheque No</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>08/04/2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DEP TFR SBI General Insurance Co Ltd</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>199.99</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>14364.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>10/05/2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>WDL TFR PMSBY RENEWAL SBISB01222</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>14344.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>25/06/2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>INTEREST CREDIT</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>97.00</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>14441.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>19/09/2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>DEBIT ATMCard AMC</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>236.00</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>14205.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>25/09/2025</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>INTEREST CREDIT</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>91.00</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>14296.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>WDL TFR PMSBY RENEWAL SBISB01222</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>14454.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Statement Summary : 01-04-2025  To  10-05-2026</t>
-        </is>
+          <t xml:space="preserve"> WDL TFR PMSBY RENEWAL SBISB09999990000000002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14454.59</v>
       </c>
     </row>
   </sheetData>

--- a/internal/importer/parser/testdata/sbi_v1.xlsx
+++ b/internal/importer/parser/testdata/sbi_v1.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,153 +413,204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A2:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Ref No/Cheque No</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Balance</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Mr. Rahul  Sharma</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Account Number  :  999900000000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IFSC Code  :  SBIN0009999</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ref No/Cheque No</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>08/04/2025</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t xml:space="preserve"> DEP TFR SBI General Insurance Co Ltd SBIGEN 99900000001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>199.99</v>
-      </c>
-      <c r="F2" t="n">
-        <v>14364.59</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 200.00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>14200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>10/05/2025</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t xml:space="preserve"> WDL TFR PMSBY RENEWAL SBISB09999990000000001</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" t="n">
-        <v>14344.59</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>14180.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>25/06/2025</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t xml:space="preserve"> INTEREST CREDIT</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>97</v>
-      </c>
-      <c r="F4" t="n">
-        <v>14441.59</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>14280.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>19/09/2025</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t xml:space="preserve"> DEBIT ATMCard AMC 999999*0000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>236</v>
-      </c>
-      <c r="F5" t="n">
-        <v>14205.59</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 200.00</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>14080.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>25/09/2025</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t xml:space="preserve"> INTEREST CREDIT</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>91</v>
-      </c>
-      <c r="F6" t="n">
-        <v>14296.59</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>14180.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t xml:space="preserve"> WDL TFR PMSBY RENEWAL SBISB09999990000000002</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
-        <v>20</v>
-      </c>
-      <c r="F7" t="n">
-        <v>14454.59</v>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>14160.00</t>
+        </is>
       </c>
     </row>
   </sheetData>
